--- a/data/Model_comparison.xlsx
+++ b/data/Model_comparison.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14390" windowHeight="11660"/>
+    <workbookView windowWidth="14190" windowHeight="11470"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -865,7 +865,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -935,6 +935,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F4F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1266,7 +1272,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
@@ -1290,16 +1296,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="5">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="6">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="5">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="7">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
@@ -1308,89 +1314,89 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="41" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="42" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="43" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="44" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1527,6 +1533,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3619,7 +3628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="13.75" hidden="1" spans="1:8">
+    <row r="2" hidden="1" spans="1:8">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -4351,7 +4360,7 @@
       <c r="C33" s="32">
         <v>85.112</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="46">
         <v>97.156</v>
       </c>
       <c r="E33" s="32" t="s">
@@ -4388,7 +4397,7 @@
       </c>
     </row>
     <row r="35" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A35" s="46">
+      <c r="A35" s="47">
         <v>34</v>
       </c>
       <c r="B35" s="21" t="s">
@@ -4411,7 +4420,7 @@
       </c>
     </row>
     <row r="36" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A36" s="46">
+      <c r="A36" s="47">
         <v>35</v>
       </c>
       <c r="B36" s="21" t="s">
@@ -4434,7 +4443,7 @@
       </c>
     </row>
     <row r="37" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A37" s="46">
+      <c r="A37" s="47">
         <v>36</v>
       </c>
       <c r="B37" s="21" t="s">
@@ -4457,7 +4466,7 @@
       </c>
     </row>
     <row r="38" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A38" s="46">
+      <c r="A38" s="47">
         <v>37</v>
       </c>
       <c r="B38" s="21" t="s">
@@ -4480,7 +4489,7 @@
       </c>
     </row>
     <row r="39" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A39" s="46">
+      <c r="A39" s="47">
         <v>38</v>
       </c>
       <c r="B39" s="21" t="s">
@@ -4503,7 +4512,7 @@
       </c>
     </row>
     <row r="40" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A40" s="46">
+      <c r="A40" s="47">
         <v>39</v>
       </c>
       <c r="B40" s="21" t="s">
@@ -4526,7 +4535,7 @@
       </c>
     </row>
     <row r="41" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A41" s="46">
+      <c r="A41" s="47">
         <v>40</v>
       </c>
       <c r="B41" s="21" t="s">
@@ -4549,7 +4558,7 @@
       </c>
     </row>
     <row r="42" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A42" s="46">
+      <c r="A42" s="47">
         <v>41</v>
       </c>
       <c r="B42" s="21" t="s">
@@ -4572,7 +4581,7 @@
       </c>
     </row>
     <row r="43" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A43" s="46">
+      <c r="A43" s="47">
         <v>42</v>
       </c>
       <c r="B43" s="21" t="s">
@@ -4595,7 +4604,7 @@
       </c>
     </row>
     <row r="44" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A44" s="46">
+      <c r="A44" s="47">
         <v>43</v>
       </c>
       <c r="B44" s="21" t="s">
@@ -4618,7 +4627,7 @@
       </c>
     </row>
     <row r="45" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A45" s="46">
+      <c r="A45" s="47">
         <v>44</v>
       </c>
       <c r="B45" s="21" t="s">
@@ -4641,7 +4650,7 @@
       </c>
     </row>
     <row r="46" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A46" s="46">
+      <c r="A46" s="47">
         <v>45</v>
       </c>
       <c r="B46" s="21" t="s">
@@ -4664,7 +4673,7 @@
       </c>
     </row>
     <row r="47" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A47" s="46">
+      <c r="A47" s="47">
         <v>46</v>
       </c>
       <c r="B47" s="21" t="s">
@@ -4687,7 +4696,7 @@
       </c>
     </row>
     <row r="48" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A48" s="46">
+      <c r="A48" s="47">
         <v>47</v>
       </c>
       <c r="B48" s="21" t="s">
@@ -4710,7 +4719,7 @@
       </c>
     </row>
     <row r="49" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A49" s="46">
+      <c r="A49" s="47">
         <v>48</v>
       </c>
       <c r="B49" s="21" t="s">
@@ -4733,7 +4742,7 @@
       </c>
     </row>
     <row r="50" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A50" s="46">
+      <c r="A50" s="47">
         <v>49</v>
       </c>
       <c r="B50" s="21" t="s">
@@ -4756,7 +4765,7 @@
       </c>
     </row>
     <row r="51" s="6" customFormat="1" spans="1:7">
-      <c r="A51" s="46">
+      <c r="A51" s="47">
         <v>50</v>
       </c>
       <c r="B51" s="18" t="s">
@@ -4765,7 +4774,7 @@
       <c r="C51" s="19">
         <v>84.414</v>
       </c>
-      <c r="D51" s="47">
+      <c r="D51" s="48">
         <v>96.976</v>
       </c>
       <c r="E51" s="19" t="s">
@@ -4779,7 +4788,7 @@
       </c>
     </row>
     <row r="52" s="6" customFormat="1" ht="26" hidden="1" spans="1:7">
-      <c r="A52" s="46">
+      <c r="A52" s="47">
         <v>51</v>
       </c>
       <c r="B52" s="21" t="s">
@@ -4802,30 +4811,30 @@
       </c>
     </row>
     <row r="53" s="6" customFormat="1" spans="1:7">
-      <c r="A53" s="46">
+      <c r="A53" s="47">
         <v>52</v>
       </c>
-      <c r="B53" s="48" t="s">
+      <c r="B53" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C53" s="49">
+      <c r="C53" s="50">
         <v>84.112</v>
       </c>
-      <c r="D53" s="50">
+      <c r="D53" s="51">
         <v>96.864</v>
       </c>
-      <c r="E53" s="49" t="s">
+      <c r="E53" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="F53" s="49">
+      <c r="F53" s="50">
         <v>20.32</v>
       </c>
-      <c r="G53" s="51" t="s">
+      <c r="G53" s="52" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="54" s="6" customFormat="1" ht="26" hidden="1" spans="1:7">
-      <c r="A54" s="46">
+      <c r="A54" s="47">
         <v>53</v>
       </c>
       <c r="B54" s="21" t="s">
@@ -4848,7 +4857,7 @@
       </c>
     </row>
     <row r="55" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A55" s="46">
+      <c r="A55" s="47">
         <v>54</v>
       </c>
       <c r="B55" s="21" t="s">
@@ -4871,7 +4880,7 @@
       </c>
     </row>
     <row r="56" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A56" s="46">
+      <c r="A56" s="47">
         <v>55</v>
       </c>
       <c r="B56" s="21" t="s">
@@ -4894,7 +4903,7 @@
       </c>
     </row>
     <row r="57" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A57" s="46">
+      <c r="A57" s="47">
         <v>56</v>
       </c>
       <c r="B57" s="21" t="s">
@@ -4917,7 +4926,7 @@
       </c>
     </row>
     <row r="58" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A58" s="46">
+      <c r="A58" s="47">
         <v>57</v>
       </c>
       <c r="B58" s="21" t="s">
@@ -4940,7 +4949,7 @@
       </c>
     </row>
     <row r="59" s="6" customFormat="1" spans="1:7">
-      <c r="A59" s="46">
+      <c r="A59" s="47">
         <v>58</v>
       </c>
       <c r="B59" s="21" t="s">
@@ -4963,7 +4972,7 @@
       </c>
     </row>
     <row r="60" s="6" customFormat="1" ht="26" hidden="1" spans="1:7">
-      <c r="A60" s="46">
+      <c r="A60" s="47">
         <v>59</v>
       </c>
       <c r="B60" s="21" t="s">
@@ -4986,7 +4995,7 @@
       </c>
     </row>
     <row r="61" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A61" s="46">
+      <c r="A61" s="47">
         <v>60</v>
       </c>
       <c r="B61" s="21" t="s">
@@ -5009,7 +5018,7 @@
       </c>
     </row>
     <row r="62" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A62" s="46">
+      <c r="A62" s="47">
         <v>61</v>
       </c>
       <c r="B62" s="21" t="s">
@@ -5032,7 +5041,7 @@
       </c>
     </row>
     <row r="63" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A63" s="46">
+      <c r="A63" s="47">
         <v>62</v>
       </c>
       <c r="B63" s="21" t="s">
@@ -5055,7 +5064,7 @@
       </c>
     </row>
     <row r="64" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A64" s="46">
+      <c r="A64" s="47">
         <v>63</v>
       </c>
       <c r="B64" s="21" t="s">
@@ -5078,7 +5087,7 @@
       </c>
     </row>
     <row r="65" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A65" s="46">
+      <c r="A65" s="47">
         <v>64</v>
       </c>
       <c r="B65" s="21" t="s">
@@ -5101,7 +5110,7 @@
       </c>
     </row>
     <row r="66" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A66" s="46">
+      <c r="A66" s="47">
         <v>65</v>
       </c>
       <c r="B66" s="21" t="s">
@@ -5124,7 +5133,7 @@
       </c>
     </row>
     <row r="67" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A67" s="46">
+      <c r="A67" s="47">
         <v>66</v>
       </c>
       <c r="B67" s="21" t="s">
@@ -5147,7 +5156,7 @@
       </c>
     </row>
     <row r="68" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A68" s="46">
+      <c r="A68" s="47">
         <v>67</v>
       </c>
       <c r="B68" s="21" t="s">
@@ -5170,7 +5179,7 @@
       </c>
     </row>
     <row r="69" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A69" s="46">
+      <c r="A69" s="47">
         <v>68</v>
       </c>
       <c r="B69" s="21" t="s">
@@ -5193,7 +5202,7 @@
       </c>
     </row>
     <row r="70" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A70" s="46">
+      <c r="A70" s="47">
         <v>69</v>
       </c>
       <c r="B70" s="21" t="s">
@@ -5216,7 +5225,7 @@
       </c>
     </row>
     <row r="71" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A71" s="46">
+      <c r="A71" s="47">
         <v>70</v>
       </c>
       <c r="B71" s="21" t="s">
@@ -5239,7 +5248,7 @@
       </c>
     </row>
     <row r="72" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A72" s="46">
+      <c r="A72" s="47">
         <v>71</v>
       </c>
       <c r="B72" s="21" t="s">
@@ -5262,7 +5271,7 @@
       </c>
     </row>
     <row r="73" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A73" s="46">
+      <c r="A73" s="47">
         <v>72</v>
       </c>
       <c r="B73" s="21" t="s">
@@ -5285,7 +5294,7 @@
       </c>
     </row>
     <row r="74" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A74" s="46">
+      <c r="A74" s="47">
         <v>73</v>
       </c>
       <c r="B74" s="21" t="s">
@@ -5308,7 +5317,7 @@
       </c>
     </row>
     <row r="75" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A75" s="46">
+      <c r="A75" s="47">
         <v>74</v>
       </c>
       <c r="B75" s="21" t="s">
@@ -5331,7 +5340,7 @@
       </c>
     </row>
     <row r="76" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A76" s="46">
+      <c r="A76" s="47">
         <v>75</v>
       </c>
       <c r="B76" s="21" t="s">
@@ -5354,7 +5363,7 @@
       </c>
     </row>
     <row r="77" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A77" s="46">
+      <c r="A77" s="47">
         <v>76</v>
       </c>
       <c r="B77" s="21" t="s">
@@ -5377,7 +5386,7 @@
       </c>
     </row>
     <row r="78" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A78" s="46">
+      <c r="A78" s="47">
         <v>77</v>
       </c>
       <c r="B78" s="21" t="s">
@@ -5400,7 +5409,7 @@
       </c>
     </row>
     <row r="79" s="6" customFormat="1" spans="1:7">
-      <c r="A79" s="46">
+      <c r="A79" s="47">
         <v>78</v>
       </c>
       <c r="B79" s="39" t="s">
@@ -5409,7 +5418,7 @@
       <c r="C79" s="40">
         <v>82.51</v>
       </c>
-      <c r="D79" s="52">
+      <c r="D79" s="53">
         <v>96.02</v>
       </c>
       <c r="E79" s="40" t="s">
@@ -5423,7 +5432,7 @@
       </c>
     </row>
     <row r="80" s="6" customFormat="1" hidden="1" spans="1:7">
-      <c r="A80" s="46">
+      <c r="A80" s="47">
         <v>79</v>
       </c>
       <c r="B80" s="21" t="s">
@@ -5446,7 +5455,7 @@
       </c>
     </row>
     <row r="81" s="6" customFormat="1" spans="1:8">
-      <c r="A81" s="46">
+      <c r="A81" s="47">
         <v>80</v>
       </c>
       <c r="B81" s="21" t="s">
@@ -5455,7 +5464,7 @@
       <c r="C81" s="22">
         <v>81.198</v>
       </c>
-      <c r="D81" s="23">
+      <c r="D81" s="46">
         <v>95.34</v>
       </c>
       <c r="E81" s="22" t="s">
@@ -5469,94 +5478,94 @@
       </c>
     </row>
     <row r="82" s="7" customFormat="1" ht="26" hidden="1" spans="1:8">
-      <c r="A82" s="53">
+      <c r="A82" s="54">
         <v>81</v>
       </c>
-      <c r="B82" s="54" t="s">
+      <c r="B82" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="C82" s="55">
+      <c r="C82" s="56">
         <v>60.552</v>
       </c>
-      <c r="D82" s="55">
+      <c r="D82" s="56">
         <v>81.746</v>
       </c>
-      <c r="E82" s="55" t="s">
+      <c r="E82" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="F82" s="55">
+      <c r="F82" s="56">
         <v>0.04</v>
       </c>
-      <c r="G82" s="56" t="s">
+      <c r="G82" s="57" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="83" s="7" customFormat="1" ht="26" hidden="1" spans="1:8">
-      <c r="A83" s="53">
+      <c r="A83" s="54">
         <v>82</v>
       </c>
-      <c r="B83" s="54" t="s">
+      <c r="B83" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="C83" s="55">
+      <c r="C83" s="56">
         <v>69.362</v>
       </c>
-      <c r="D83" s="55">
+      <c r="D83" s="56">
         <v>88.316</v>
       </c>
-      <c r="E83" s="55" t="s">
+      <c r="E83" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="F83" s="55">
+      <c r="F83" s="56">
         <v>0.14</v>
       </c>
-      <c r="G83" s="56" t="s">
+      <c r="G83" s="57" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="84" s="7" customFormat="1" ht="26" hidden="1" spans="1:8">
-      <c r="A84" s="53">
+      <c r="A84" s="54">
         <v>83</v>
       </c>
-      <c r="B84" s="54" t="s">
+      <c r="B84" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="C84" s="55">
+      <c r="C84" s="56">
         <v>72.996</v>
       </c>
-      <c r="D84" s="55">
+      <c r="D84" s="56">
         <v>91.086</v>
       </c>
-      <c r="E84" s="55" t="s">
+      <c r="E84" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="F84" s="55">
+      <c r="F84" s="56">
         <v>0.3</v>
       </c>
-      <c r="G84" s="56" t="s">
+      <c r="G84" s="57" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="85" s="7" customFormat="1" ht="26" hidden="1" spans="1:8">
-      <c r="A85" s="53">
+      <c r="A85" s="54">
         <v>84</v>
       </c>
-      <c r="B85" s="54" t="s">
+      <c r="B85" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="C85" s="55">
+      <c r="C85" s="56">
         <v>76.23</v>
       </c>
-      <c r="D85" s="55">
+      <c r="D85" s="56">
         <v>93.006</v>
       </c>
-      <c r="E85" s="55" t="s">
+      <c r="E85" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="F85" s="55">
+      <c r="F85" s="56">
         <v>0.58</v>
       </c>
-      <c r="G85" s="56" t="s">
+      <c r="G85" s="57" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5607,25 +5616,25 @@
       </c>
     </row>
     <row r="88" s="8" customFormat="1" hidden="1" spans="1:8">
-      <c r="A88" s="57">
+      <c r="A88" s="58">
         <v>87</v>
       </c>
-      <c r="B88" s="48" t="s">
+      <c r="B88" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="C88" s="49">
+      <c r="C88" s="50">
         <v>83.582</v>
       </c>
-      <c r="D88" s="49">
+      <c r="D88" s="50">
         <v>96.64</v>
       </c>
-      <c r="E88" s="49" t="s">
+      <c r="E88" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="F88" s="49">
+      <c r="F88" s="50">
         <v>15.43</v>
       </c>
-      <c r="G88" s="51" t="s">
+      <c r="G88" s="52" t="s">
         <v>10</v>
       </c>
       <c r="H88" s="8" t="s">
@@ -5633,53 +5642,53 @@
       </c>
     </row>
     <row r="89" s="8" customFormat="1" hidden="1" spans="1:8">
-      <c r="A89" s="57">
+      <c r="A89" s="58">
         <v>88</v>
       </c>
-      <c r="B89" s="48" t="s">
+      <c r="B89" s="49" t="s">
         <v>158</v>
       </c>
-      <c r="C89" s="49">
+      <c r="C89" s="50">
         <v>83.196</v>
       </c>
-      <c r="D89" s="49">
+      <c r="D89" s="50">
         <v>96.36</v>
       </c>
-      <c r="E89" s="49" t="s">
+      <c r="E89" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="F89" s="49">
+      <c r="F89" s="50">
         <v>8.74</v>
       </c>
-      <c r="G89" s="51" t="s">
+      <c r="G89" s="52" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="90" s="8" customFormat="1" hidden="1" spans="1:8">
-      <c r="A90" s="57">
+      <c r="A90" s="58">
         <v>89</v>
       </c>
-      <c r="B90" s="48" t="s">
+      <c r="B90" s="49" t="s">
         <v>160</v>
       </c>
-      <c r="C90" s="49">
+      <c r="C90" s="50">
         <v>81.474</v>
       </c>
-      <c r="D90" s="49">
+      <c r="D90" s="50">
         <v>95.776</v>
       </c>
-      <c r="E90" s="49" t="s">
+      <c r="E90" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="F90" s="49">
+      <c r="F90" s="50">
         <v>4.49</v>
       </c>
-      <c r="G90" s="51" t="s">
+      <c r="G90" s="52" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" s="8" customFormat="1" spans="1:8">
-      <c r="A91" s="57">
+      <c r="A91" s="58">
         <v>90</v>
       </c>
       <c r="B91" s="26" t="s">
@@ -5688,7 +5697,7 @@
       <c r="C91" s="29">
         <v>77.138</v>
       </c>
-      <c r="D91" s="29">
+      <c r="D91" s="46">
         <v>93.56</v>
       </c>
       <c r="E91" s="27" t="s">
@@ -5702,223 +5711,223 @@
       </c>
     </row>
     <row r="92" s="8" customFormat="1" hidden="1" spans="1:8">
-      <c r="A92" s="57">
+      <c r="A92" s="58">
         <v>91</v>
       </c>
-      <c r="B92" s="48" t="s">
+      <c r="B92" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="C92" s="49">
+      <c r="C92" s="50">
         <v>83.712</v>
       </c>
-      <c r="D92" s="49">
+      <c r="D92" s="50">
         <v>96.816</v>
       </c>
-      <c r="E92" s="49" t="s">
+      <c r="E92" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="F92" s="49">
+      <c r="F92" s="50">
         <v>11.55</v>
       </c>
-      <c r="G92" s="51" t="s">
+      <c r="G92" s="52" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="93" s="8" customFormat="1" hidden="1" spans="1:8">
-      <c r="A93" s="57">
+      <c r="A93" s="58">
         <v>92</v>
       </c>
-      <c r="B93" s="48" t="s">
+      <c r="B93" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="C93" s="49">
+      <c r="C93" s="50">
         <v>82.072</v>
       </c>
-      <c r="D93" s="49">
+      <c r="D93" s="50">
         <v>96.132</v>
       </c>
-      <c r="E93" s="49" t="s">
+      <c r="E93" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="F93" s="49">
+      <c r="F93" s="50">
         <v>5.94</v>
       </c>
-      <c r="G93" s="51" t="s">
+      <c r="G93" s="52" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="94" s="9" customFormat="1" hidden="1" spans="1:8">
-      <c r="A94" s="58">
+      <c r="A94" s="59">
         <v>93</v>
       </c>
-      <c r="B94" s="59" t="s">
+      <c r="B94" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="C94" s="60">
+      <c r="C94" s="61">
         <v>70.37</v>
       </c>
-      <c r="D94" s="60">
+      <c r="D94" s="61">
         <v>89.81</v>
       </c>
-      <c r="E94" s="60" t="s">
+      <c r="E94" s="61" t="s">
         <v>169</v>
       </c>
-      <c r="F94" s="60">
+      <c r="F94" s="61">
         <v>7.61</v>
       </c>
-      <c r="G94" s="61" t="s">
+      <c r="G94" s="62" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="95" s="9" customFormat="1" hidden="1" spans="1:8">
-      <c r="A95" s="58">
+      <c r="A95" s="59">
         <v>94</v>
       </c>
-      <c r="B95" s="59" t="s">
+      <c r="B95" s="60" t="s">
         <v>170</v>
       </c>
-      <c r="C95" s="60">
+      <c r="C95" s="61">
         <v>69.02</v>
       </c>
-      <c r="D95" s="60">
+      <c r="D95" s="61">
         <v>88.628</v>
       </c>
-      <c r="E95" s="60" t="s">
+      <c r="E95" s="61" t="s">
         <v>169</v>
       </c>
-      <c r="F95" s="60">
+      <c r="F95" s="61">
         <v>7.61</v>
       </c>
-      <c r="G95" s="61" t="s">
+      <c r="G95" s="62" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="96" s="9" customFormat="1" hidden="1" spans="1:8">
-      <c r="A96" s="58">
+      <c r="A96" s="59">
         <v>95</v>
       </c>
-      <c r="B96" s="59" t="s">
+      <c r="B96" s="60" t="s">
         <v>171</v>
       </c>
-      <c r="C96" s="60">
+      <c r="C96" s="61">
         <v>71.586</v>
       </c>
-      <c r="D96" s="60">
+      <c r="D96" s="61">
         <v>90.374</v>
       </c>
-      <c r="E96" s="60" t="s">
+      <c r="E96" s="61" t="s">
         <v>172</v>
       </c>
-      <c r="F96" s="60">
+      <c r="F96" s="61">
         <v>11.31</v>
       </c>
-      <c r="G96" s="61" t="s">
+      <c r="G96" s="62" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="97" s="9" customFormat="1" hidden="1" spans="1:8">
-      <c r="A97" s="58">
+      <c r="A97" s="59">
         <v>96</v>
       </c>
-      <c r="B97" s="59" t="s">
+      <c r="B97" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="C97" s="60">
+      <c r="C97" s="61">
         <v>69.928</v>
       </c>
-      <c r="D97" s="60">
+      <c r="D97" s="61">
         <v>89.246</v>
       </c>
-      <c r="E97" s="60" t="s">
+      <c r="E97" s="61" t="s">
         <v>174</v>
       </c>
-      <c r="F97" s="60">
+      <c r="F97" s="61">
         <v>11.31</v>
       </c>
-      <c r="G97" s="61" t="s">
+      <c r="G97" s="62" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="98" s="9" customFormat="1" hidden="1" spans="1:8">
-      <c r="A98" s="58">
+      <c r="A98" s="59">
         <v>97</v>
       </c>
-      <c r="B98" s="59" t="s">
+      <c r="B98" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="C98" s="60">
+      <c r="C98" s="61">
         <v>73.36</v>
       </c>
-      <c r="D98" s="60">
+      <c r="D98" s="61">
         <v>91.516</v>
       </c>
-      <c r="E98" s="60" t="s">
+      <c r="E98" s="61" t="s">
         <v>176</v>
       </c>
-      <c r="F98" s="60">
+      <c r="F98" s="61">
         <v>15.47</v>
       </c>
-      <c r="G98" s="61" t="s">
+      <c r="G98" s="62" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="99" s="9" customFormat="1" hidden="1" spans="1:8">
-      <c r="A99" s="58">
+      <c r="A99" s="59">
         <v>98</v>
       </c>
-      <c r="B99" s="59" t="s">
+      <c r="B99" s="60" t="s">
         <v>177</v>
       </c>
-      <c r="C99" s="60" t="s">
+      <c r="C99" s="61" t="s">
         <v>178</v>
       </c>
-      <c r="D99" s="60" t="s">
+      <c r="D99" s="61" t="s">
         <v>178</v>
       </c>
-      <c r="E99" s="60" t="s">
+      <c r="E99" s="61" t="s">
         <v>176</v>
       </c>
-      <c r="F99" s="60">
+      <c r="F99" s="61">
         <v>15.47</v>
       </c>
-      <c r="G99" s="61" t="s">
+      <c r="G99" s="62" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="100" s="9" customFormat="1" hidden="1" spans="1:8">
-      <c r="A100" s="58">
+      <c r="A100" s="59">
         <v>99</v>
       </c>
-      <c r="B100" s="59" t="s">
+      <c r="B100" s="60" t="s">
         <v>179</v>
       </c>
-      <c r="C100" s="60">
+      <c r="C100" s="61">
         <v>71.592</v>
       </c>
-      <c r="D100" s="60">
+      <c r="D100" s="61">
         <v>90.382</v>
       </c>
-      <c r="E100" s="60" t="s">
+      <c r="E100" s="61" t="s">
         <v>176</v>
       </c>
-      <c r="F100" s="60">
+      <c r="F100" s="61">
         <v>15.47</v>
       </c>
-      <c r="G100" s="61" t="s">
+      <c r="G100" s="62" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="101" s="9" customFormat="1" spans="1:8">
-      <c r="A101" s="58">
+      <c r="A101" s="59">
         <v>100</v>
       </c>
       <c r="B101" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="C101" s="52">
+      <c r="C101" s="53">
         <v>76.506</v>
       </c>
-      <c r="D101" s="52">
+      <c r="D101" s="53">
         <v>93.522</v>
       </c>
       <c r="E101" s="40" t="s">
@@ -5932,25 +5941,25 @@
       </c>
     </row>
     <row r="102" s="9" customFormat="1" hidden="1" spans="1:8">
-      <c r="A102" s="58">
+      <c r="A102" s="59">
         <v>101</v>
       </c>
-      <c r="B102" s="59" t="s">
+      <c r="B102" s="60" t="s">
         <v>182</v>
       </c>
-      <c r="C102" s="60">
+      <c r="C102" s="61">
         <v>72.376</v>
       </c>
-      <c r="D102" s="60">
+      <c r="D102" s="61">
         <v>90.876</v>
       </c>
-      <c r="E102" s="60" t="s">
+      <c r="E102" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="F102" s="60">
+      <c r="F102" s="61">
         <v>19.63</v>
       </c>
-      <c r="G102" s="61" t="s">
+      <c r="G102" s="62" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6102,10 +6111,10 @@
       <c r="B109" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="C109" s="62">
+      <c r="C109" s="63">
         <v>75.274</v>
       </c>
-      <c r="D109" s="62">
+      <c r="D109" s="46">
         <v>92.566</v>
       </c>
       <c r="E109" s="44" t="s">
@@ -6214,22 +6223,22 @@
       <c r="A114" s="38">
         <v>113</v>
       </c>
-      <c r="B114" s="59" t="s">
+      <c r="B114" s="60" t="s">
         <v>203</v>
       </c>
-      <c r="C114" s="63">
+      <c r="C114" s="64">
         <v>74.218</v>
       </c>
-      <c r="D114" s="63">
+      <c r="D114" s="64">
         <v>91.842</v>
       </c>
-      <c r="E114" s="60" t="s">
+      <c r="E114" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="F114" s="60">
+      <c r="F114" s="61">
         <v>19.63</v>
       </c>
-      <c r="G114" s="61" t="s">
+      <c r="G114" s="62" t="s">
         <v>10</v>
       </c>
     </row>
